--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/pre LAM_HRM-2031-0240/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/pre LAM_HRM-2031-0240/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.2827</v>
+        <v>17.42562</v>
       </c>
       <c r="D2" t="n">
-        <v>17.57511</v>
+        <v>17.38794</v>
       </c>
       <c r="E2" t="n">
-        <v>17.8325</v>
+        <v>17.41732</v>
       </c>
       <c r="F2" t="n">
-        <v>44.675</v>
+        <v>44.72188</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0532</v>
+        <v>0.05275</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9183</v>
+        <v>1.88495</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.72766</v>
+        <v>18.08747</v>
       </c>
       <c r="D3" t="n">
-        <v>17.25792</v>
+        <v>17.30694</v>
       </c>
       <c r="E3" t="n">
-        <v>17.19235</v>
+        <v>17.48022</v>
       </c>
       <c r="F3" t="n">
-        <v>44.49284</v>
+        <v>44.78176</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05395</v>
+        <v>0.0533</v>
       </c>
       <c r="H3" t="n">
-        <v>1.88444</v>
+        <v>1.9117</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.19943</v>
+        <v>17.57669</v>
       </c>
       <c r="D4" t="n">
-        <v>17.27382</v>
+        <v>17.18875</v>
       </c>
       <c r="E4" t="n">
-        <v>17.42983</v>
+        <v>17.3824</v>
       </c>
       <c r="F4" t="n">
-        <v>44.16425</v>
+        <v>44.0976</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05266</v>
+        <v>0.05224</v>
       </c>
       <c r="H4" t="n">
-        <v>1.89901</v>
+        <v>1.90445</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.45249</v>
+        <v>17.82079</v>
       </c>
       <c r="D6" t="n">
-        <v>16.8032</v>
+        <v>16.58516</v>
       </c>
       <c r="E6" t="n">
-        <v>17.36255</v>
+        <v>17.25716</v>
       </c>
       <c r="F6" t="n">
-        <v>22.8777</v>
+        <v>22.81127</v>
       </c>
       <c r="G6" t="n">
-        <v>35.34017</v>
+        <v>36.27532</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.12077</v>
+        <v>18.04678</v>
       </c>
       <c r="D7" t="n">
-        <v>16.40288</v>
+        <v>16.91297</v>
       </c>
       <c r="E7" t="n">
-        <v>16.76223</v>
+        <v>17.09518</v>
       </c>
       <c r="F7" t="n">
-        <v>23.37404</v>
+        <v>22.4568</v>
       </c>
       <c r="G7" t="n">
-        <v>36.03259</v>
+        <v>35.7959</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.74597</v>
+        <v>17.32495</v>
       </c>
       <c r="D8" t="n">
-        <v>16.47682</v>
+        <v>16.59844</v>
       </c>
       <c r="E8" t="n">
-        <v>17.08539</v>
+        <v>17.01997</v>
       </c>
       <c r="F8" t="n">
-        <v>22.90662</v>
+        <v>22.43302</v>
       </c>
       <c r="G8" t="n">
-        <v>36.19775</v>
+        <v>35.56711</v>
       </c>
     </row>
   </sheetData>
